--- a/KatalonData/RADTestData/EmailNoMatch.xlsx
+++ b/KatalonData/RADTestData/EmailNoMatch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{3BBEFFBE-0554-443D-894A-37775305B1B5}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{774FB53A-7EF6-4BA2-816E-3A737DE40096}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="15840" windowWidth="29040" xWindow="28680" xr2:uid="{8832F8CD-C84D-4F68-8EAE-C2E28DFA491F}" yWindow="-3945"/>
+    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{8832F8CD-C84D-4F68-8EAE-C2E28DFA491F}" yWindow="2952"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="149">
   <si>
     <t>Execute</t>
   </si>
@@ -138,508 +138,349 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 22:49:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:50:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:50:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:50:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:50:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:50:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:51:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:51:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:51:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:51:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:51:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:52:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:52:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:52:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:52:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:53:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:53:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:53:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:53:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:54:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:54:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:54:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:54:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:55:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:55:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:55:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:55:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:55:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:56:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:56:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:56:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:56:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:57:03 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 22:57:15 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 22:57:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:57:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:57:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:58:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:58:25 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 22:58:53 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 22:59:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:59:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:59:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:59:48 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:00:01 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:00:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:00:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:00:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:01:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:01:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:01:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:01:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:02:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:02:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:02:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:02:40 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:02:53 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:03:06 EST 2025</t>
-  </si>
-  <si>
     <t>DoNotRun</t>
   </si>
   <si>
+    <t>Thu May 14 16:43:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:44:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:44:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:44:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:44:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:44:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:44:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:45:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:45:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:45:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:45:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:45:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:46:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:46:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:46:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:46:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:46:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:46:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:47:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:47:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:47:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:47:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:47:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:47:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:48:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:48:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:48:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:48:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:48:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:49:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:49:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:49:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:49:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:49:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:50:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:50:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:50:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:50:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:50:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:50:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:51:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:51:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:51:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:51:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:51:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:52:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:52:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:52:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:52:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:52:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:53:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:53:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:53:22 EDT 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Sat Oct 04 16:12:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:13:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:14:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:15:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:09 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:16:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:10 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:17:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:18:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:10:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:11:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:12:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:13:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:14:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:15:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:28 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:16:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:17:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:17:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:17:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 14:17:27 EST 2025</t>
+    <t>Thu May 21 23:05:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:05:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:06:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:07:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:07:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:07:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:07:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:07:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:08:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:08:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:08:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:08:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:08:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:08:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:09:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:09:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:09:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:09:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:09:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:09:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:10:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:11:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:11:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:11:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:11:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:11:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:11:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:12:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:13:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:14:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:14:09 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1010,18 +851,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2750B36-BDE9-40E0-AADF-384378C45A8A}">
-  <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="34.7265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="47.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="43.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="34.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1038,12 +879,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -1055,12 +896,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -1072,12 +913,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1089,12 +930,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -1106,12 +947,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -1123,12 +964,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -1140,12 +981,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1157,12 +998,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -1174,12 +1015,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1191,12 +1032,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1208,12 +1049,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1225,12 +1066,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1242,12 +1083,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1259,12 +1100,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1276,12 +1117,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1293,12 +1134,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1310,12 +1151,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1327,12 +1168,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1344,12 +1185,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1361,12 +1202,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1378,12 +1219,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1395,12 +1236,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1412,12 +1253,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1429,12 +1270,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1446,12 +1287,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1463,12 +1304,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1480,12 +1321,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1497,12 +1338,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1514,12 +1355,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1531,12 +1372,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1548,12 +1389,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1565,12 +1406,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1582,12 +1423,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1599,15 +1440,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>31</v>
@@ -1616,12 +1457,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -1633,12 +1474,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1650,12 +1491,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1667,12 +1508,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1684,12 +1525,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1701,15 +1542,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
@@ -1718,12 +1559,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1735,12 +1576,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1752,12 +1593,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1769,12 +1610,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1786,15 +1627,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>7</v>
@@ -1803,12 +1644,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>136</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1820,12 +1661,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1837,12 +1678,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1854,12 +1695,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1871,12 +1712,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -1888,12 +1729,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -1905,12 +1746,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1922,12 +1763,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1939,12 +1780,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1956,12 +1797,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1973,12 +1814,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
@@ -1990,15 +1831,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>7</v>
@@ -2007,12 +1848,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -2022,6 +1863,23 @@
       </c>
       <c r="E59" s="1" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/RADTestData/EmailNoMatch.xlsx
+++ b/KatalonData/RADTestData/EmailNoMatch.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{774FB53A-7EF6-4BA2-816E-3A737DE40096}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5491038E-63DD-4C14-A9E1-085D862553C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{8832F8CD-C84D-4F68-8EAE-C2E28DFA491F}" yWindow="2952"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8832F8CD-C84D-4F68-8EAE-C2E28DFA491F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="144">
   <si>
     <t>Execute</t>
   </si>
@@ -138,349 +138,334 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 22:57:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:58:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:00:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:02:53 EST 2025</t>
-  </si>
-  <si>
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Thu May 14 16:43:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:44:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:44:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:44:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:44:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:44:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:44:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:45:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:45:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:45:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:45:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:45:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:46:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:46:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:46:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:46:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:46:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:46:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:47:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:47:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:47:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:47:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:47:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:47:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:48:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:48:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:48:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:48:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:48:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:49:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:49:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:49:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:49:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:49:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:50:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:50:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:50:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:50:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:50:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:50:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:51:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:51:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:51:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:51:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:51:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:52:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:52:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:52:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:52:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:52:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:53:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:53:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:53:22 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu May 21 23:05:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:05:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:06:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:07:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:07:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:07:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:07:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:07:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:08:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:08:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:08:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:08:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:08:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:08:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:09:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:09:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:09:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:09:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:09:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:09:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:10:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:11:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:11:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:11:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:11:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:11:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:11:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:12:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:13:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:14:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:14:09 EDT 2026</t>
+    <t>Wed Jun 24 23:34:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:34:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:34:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:34:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:34:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:34:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:35:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:36:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:37:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:37:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:37:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:37:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:37:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:37:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:38:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:38:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:38:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:38:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:38:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:38:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:39:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:39:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:39:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:39:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:39:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:39:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:40:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:40:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:40:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:40:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:40:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:40:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:41:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:41:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:41:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:41:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:41:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:41:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:42:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:40:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:40:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:40:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:34:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:35:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:36:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:36:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:36:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:36:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:36:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:36:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:37:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:38:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:39:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:40:52 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -530,19 +515,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -559,10 +544,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -597,7 +582,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -649,7 +634,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -760,21 +745,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -791,7 +776,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -843,15 +828,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2750B36-BDE9-40E0-AADF-384378C45A8A}">
-  <dimension ref="A1:F60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2750B36-BDE9-40E0-AADF-384378C45A8A}">
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
@@ -880,11 +865,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>94</v>
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -897,11 +882,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>95</v>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -914,11 +899,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>96</v>
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -931,11 +916,11 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>97</v>
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -948,11 +933,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>98</v>
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -965,11 +950,11 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>99</v>
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -982,11 +967,11 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>100</v>
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -999,11 +984,11 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>101</v>
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -1016,11 +1001,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>102</v>
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1033,11 +1018,11 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1050,11 +1035,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>104</v>
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1067,11 +1052,11 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>105</v>
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1084,11 +1069,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>106</v>
+      <c r="A14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1101,11 +1086,11 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>107</v>
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1118,11 +1103,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
-        <v>108</v>
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1135,11 +1120,11 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1152,11 +1137,11 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>110</v>
+      <c r="A18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1169,11 +1154,11 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" t="s">
-        <v>111</v>
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1186,11 +1171,11 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s">
-        <v>112</v>
+      <c r="A20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1203,11 +1188,11 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" t="s">
-        <v>113</v>
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1220,11 +1205,11 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
-        <v>114</v>
+      <c r="A22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1237,11 +1222,11 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>115</v>
+      <c r="A23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1254,11 +1239,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>116</v>
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1271,11 +1256,11 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>117</v>
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1288,11 +1273,11 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>118</v>
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1305,11 +1290,11 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>119</v>
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1322,11 +1307,11 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" t="s">
-        <v>120</v>
+      <c r="A28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1339,11 +1324,11 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" t="s">
-        <v>121</v>
+      <c r="A29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1356,11 +1341,11 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" t="s">
-        <v>122</v>
+      <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1373,11 +1358,11 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" t="s">
-        <v>123</v>
+      <c r="A31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1390,11 +1375,11 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" t="s">
-        <v>124</v>
+      <c r="A32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1407,11 +1392,11 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" t="s">
-        <v>125</v>
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1424,11 +1409,11 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" t="s">
-        <v>126</v>
+      <c r="A34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1441,14 +1426,8 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C35" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>31</v>
@@ -1458,11 +1437,11 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" t="s">
-        <v>127</v>
+      <c r="A36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -1475,11 +1454,11 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" t="s">
-        <v>128</v>
+      <c r="A37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1492,11 +1471,11 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" t="s">
-        <v>129</v>
+      <c r="A38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1509,11 +1488,11 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" t="s">
-        <v>130</v>
+      <c r="A39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1526,11 +1505,11 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" t="s">
-        <v>131</v>
+      <c r="A40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1543,14 +1522,8 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
       <c r="C41" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
@@ -1560,11 +1533,11 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" t="s">
-        <v>132</v>
+      <c r="A42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1577,11 +1550,11 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" t="s">
-        <v>133</v>
+      <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1594,11 +1567,11 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
-        <v>134</v>
+      <c r="A44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1611,11 +1584,11 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" t="s">
-        <v>135</v>
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1628,14 +1601,8 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" t="s">
-        <v>36</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>7</v>
@@ -1645,11 +1612,11 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" t="s">
-        <v>136</v>
+      <c r="A47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1662,11 +1629,11 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" t="s">
-        <v>137</v>
+      <c r="A48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1679,11 +1646,11 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" t="s">
-        <v>138</v>
+      <c r="A49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1696,11 +1663,11 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" t="s">
-        <v>139</v>
+      <c r="A50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1713,11 +1680,11 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" t="s">
-        <v>140</v>
+      <c r="A51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -1730,11 +1697,11 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>5</v>
-      </c>
-      <c r="B52" t="s">
-        <v>141</v>
+      <c r="A52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -1747,11 +1714,11 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>5</v>
-      </c>
-      <c r="B53" t="s">
-        <v>142</v>
+      <c r="A53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1764,11 +1731,11 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>5</v>
-      </c>
-      <c r="B54" t="s">
-        <v>143</v>
+      <c r="A54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1781,11 +1748,11 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>5</v>
-      </c>
-      <c r="B55" t="s">
-        <v>144</v>
+      <c r="A55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1798,11 +1765,11 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" t="s">
-        <v>145</v>
+      <c r="A56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1815,14 +1782,8 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>5</v>
-      </c>
-      <c r="B57" t="s">
-        <v>146</v>
-      </c>
       <c r="C57" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>31</v>
@@ -1832,14 +1793,8 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" t="s">
-        <v>37</v>
-      </c>
       <c r="C58" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>7</v>
@@ -1849,14 +1804,8 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" t="s">
-        <v>147</v>
-      </c>
       <c r="C59" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>7</v>
@@ -1866,11 +1815,11 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>148</v>
+      <c r="A60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -1882,9 +1831,26 @@
         <v>32</v>
       </c>
     </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s" s="1">
+        <v>143</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>

--- a/KatalonData/RADTestData/EmailNoMatch.xlsx
+++ b/KatalonData/RADTestData/EmailNoMatch.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5491038E-63DD-4C14-A9E1-085D862553C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A24162-59BE-4015-89E1-B771CEF0EDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8832F8CD-C84D-4F68-8EAE-C2E28DFA491F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>Execute</t>
   </si>
@@ -141,171 +141,9 @@
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Wed Jun 24 23:34:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:34:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:34:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:34:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:34:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:34:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:35:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:36:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:37:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:37:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:37:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:37:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:37:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:37:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:38:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:38:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:38:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:38:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:38:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:38:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:39:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:39:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:39:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:39:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:39:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:39:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:40:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:40:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:40:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:40:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:40:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:40:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:41:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:41:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:41:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:41:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:41:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:41:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:42:07 EDT 2026</t>
-  </si>
-  <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
-    <t>Thu Jul 09 17:40:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:40:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 17:40:48 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jul 09 22:33:11 EDT 2026</t>
   </si>
   <si>
@@ -466,13 +304,18 @@
   </si>
   <si>
     <t>Thu Jul 09 22:40:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 19:10:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 03 15:34:49 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -839,12 +682,12 @@
   <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="34.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="34.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="47.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -869,7 +712,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -886,7 +729,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -903,7 +746,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -920,7 +763,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -937,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -954,7 +797,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -971,7 +814,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -988,7 +831,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -1005,7 +848,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1022,7 +865,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1039,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1056,7 +899,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1073,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1090,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1107,7 +950,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1124,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -1141,7 +984,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1158,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1175,7 +1018,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1192,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1209,7 +1052,7 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1226,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1243,7 +1086,7 @@
         <v>5</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1260,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1277,7 +1120,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1294,7 +1137,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1311,7 +1154,7 @@
         <v>5</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1328,7 +1171,7 @@
         <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1345,7 +1188,7 @@
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1362,7 +1205,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1379,7 +1222,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1396,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1413,7 +1256,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1441,7 +1284,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -1458,7 +1301,7 @@
         <v>5</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1475,7 +1318,7 @@
         <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1492,7 +1335,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1509,7 +1352,7 @@
         <v>5</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1537,7 +1380,7 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1554,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1571,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1588,7 +1431,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1601,8 +1444,14 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
       <c r="C46" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>7</v>
@@ -1616,7 +1465,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1633,7 +1482,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1650,7 +1499,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1667,7 +1516,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1684,7 +1533,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -1701,7 +1550,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -1718,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1735,7 +1584,7 @@
         <v>5</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1752,7 +1601,7 @@
         <v>5</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -1769,7 +1618,7 @@
         <v>5</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1804,8 +1653,14 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C59" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>7</v>
@@ -1819,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -1835,8 +1690,8 @@
       <c r="A61" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B61" t="s" s="1">
-        <v>143</v>
+      <c r="B61" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
@@ -1845,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
